--- a/VBCS Credentials.xlsx
+++ b/VBCS Credentials.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{8025FF17-D174-43B9-BD68-99AC6C9EA1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="1470" windowWidth="21600" windowHeight="11295" xr2:uid="{17C3B3CA-E990-4C55-86C4-B6AE7F10E11B}"/>
+    <workbookView xWindow="5235" yWindow="2280" windowWidth="21600" windowHeight="11295" xr2:uid="{17C3B3CA-E990-4C55-86C4-B6AE7F10E11B}"/>
   </bookViews>
   <sheets>
     <sheet name="IWP (2)" sheetId="1" r:id="rId1"/>
